--- a/specification_UZ95-039-045-2026.xlsx
+++ b/specification_UZ95-039-045-2026.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">9015 90 — части и принадлежности; товар — готовый прибор (зам. 7)</t>
   </si>
   <si>
-    <t xml:space="preserve">Неясное слово «КЛЕЩЕ» (зам. 9); код 9015 90 — части и принадлежности (зам. 7)</t>
+    <t xml:space="preserve">Неясное слово «КЛЕШЕ» (зам. 9); код 9015 90 — части и принадлежности (зам. 7)</t>
   </si>
   <si>
     <t xml:space="preserve">Опечатка: верно «ЭЛЕКТРОПНЕВМАТИЧЕСКИЙ» — перенесено как в оригинале (зам. 8)</t>
@@ -366,7 +366,7 @@
     <t xml:space="preserve">PATRON REPARADO/CALIBRADO</t>
   </si>
   <si>
-    <t xml:space="preserve">КЛЕЩЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ</t>
+    <t xml:space="preserve">КЛЕШЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ</t>
   </si>
   <si>
     <t xml:space="preserve">UZ95-043-2026</t>
@@ -810,7 +810,7 @@
     <t xml:space="preserve">Z10063008, Z594470</t>
   </si>
   <si>
-    <t xml:space="preserve">Код 9015900000 — субпозиция 9015 90 «части и принадлежности». «ЦИФРОВОЙ ИНКЛИНОМЕТР» — законченный прибор, а не часть (возможно, 9015 80). Назначение Z594470 «КЛЕЩЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ» (исп. PATRON — эталон/шаблон) из документов неясно.</t>
+    <t xml:space="preserve">Код 9015900000 — субпозиция 9015 90 «части и принадлежности». «ЦИФРОВОЙ ИНКЛИНОМЕТР» — законченный прибор, а не часть (возможно, 9015 80). Назначение Z594470 «КЛЕШЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ» (исп. PATRON — эталон/шаблон) из документов неясно.</t>
   </si>
   <si>
     <t xml:space="preserve">Коды перенесены как в документе.</t>
@@ -831,13 +831,13 @@
     <t xml:space="preserve">Неясное наименование</t>
   </si>
   <si>
-    <t xml:space="preserve">«КЛЕЩЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ» — «КЛЕЩЕ» не является корректной словоформой (возможно, имелось в виду «КЛЕЩИ»). Исп.: PATRON REPARADO/CALIBRADO — эталон (шаблон) отремонтированный/откалиброванный.</t>
+    <t xml:space="preserve">«КЛЕШЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ» — слова «КЛЕШЕ» в русском языке нет. Возможно, имелось в виду «КЛИШЕ» (шаблон), что согласуется с исп. описанием, но это предположение. Исп.: PATRON REPARADO/CALIBRADO — эталон (шаблон) отремонтированный/откалиброванный.</t>
   </si>
   <si>
     <t xml:space="preserve">Перенесено как в оригинале; уточнить у отправителя.</t>
   </si>
   <si>
-    <t xml:space="preserve">Высокая — в части факта; что имелось в виду, я не знаю</t>
+    <t xml:space="preserve">Высокая — написание подтверждено повторной независимой проверкой скана; версия «КЛИШЕ» — предположение</t>
   </si>
   <si>
     <t xml:space="preserve">Расчёт (не из документа)</t>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D18" s="6" t="str">
         <f aca="false">'Исходные данные'!K18</f>
-        <v>КЛЕЩЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ</v>
+        <v>КЛЕШЕ (ПАТРОН) КАЛИБРОВОЧНЫЙ</v>
       </c>
       <c r="E18" s="5" t="str">
         <f aca="false">'Исходные данные'!M18</f>

--- a/specification_UZ95-039-045-2026.xlsx
+++ b/specification_UZ95-039-045-2026.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="288">
   <si>
     <t xml:space="preserve">Спецификация товаров по счетам-проформам UZ95-039-2026 … UZ95-045-2026 от 21.09.2026 и упаковочным листам к ним</t>
   </si>
@@ -123,6 +123,9 @@
     <t xml:space="preserve">Синий шрифт — значения, перенесённые из документов (файл 8c38d916-supporting_4.pdf, стр. указаны в столбце C). Чёрный — формулы. Столбцы W–Z: распределение веса брутто места по позициям пропорционально весу нетто (округление до 0,01 кг; остаток округления относится на позицию с наибольшим весом нетто в месте).</t>
   </si>
   <si>
+    <t xml:space="preserve">Важно: значения PL для артикула, наименования и количества (столбцы I, L, O) введены один раз и равны значениям счёта — они были сверены с упаковочными листами визуально и при независимой повторной перечитке сканов. Поэтому проверки в столбцах AC–AE здесь всегда «OK» по построению и сами по себе ничего не доказывают.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Стр. PDF (счёт / PL)</t>
   </si>
   <si>
@@ -720,7 +723,7 @@
     <t xml:space="preserve">Замечания аудитора по комплекту документов</t>
   </si>
   <si>
-    <t xml:space="preserve">Коды ТН ВЭД перенесены строго как в документах. Комментарии к классификации сделаны на уровне 6 знаков ГС по текстам товарных позиций/субпозиций; национальные знаки (7–10) не проверялись — нет доступа к актуальной редакции тарифа. Окончательное решение о классификации — за декларантом.</t>
+    <t xml:space="preserve">Коды ТН ВЭД перенесены строго как в документах. Комментарии к классификации сделаны ИИ-ассистентом по общим сведениям о структуре ГС на уровне 6 знаков, БЕЗ сверки с текстом действующего ТН ВЭД и пояснений к нему; национальные знаки (7–10) не проверялись. Это поводы для проверки, а не заключения. Окончательное решение о классификации — за декларантом.</t>
   </si>
   <si>
     <t xml:space="preserve">Уровень</t>
@@ -905,7 +908,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
     <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,6 +970,14 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF9A3412"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1080,7 +1091,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1153,31 +1164,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1337,7 +1352,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF9A3412"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -3466,6 +3481,26 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
     </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+    </row>
     <row r="4" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>3</v>
@@ -3474,159 +3509,159 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="C5" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="20" t="str">
+      <c r="E5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="21" t="str">
         <f aca="false">B5&amp;" | место "&amp;E5</f>
         <v>UZ95-039-2026 | место 1</v>
       </c>
-      <c r="H5" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="21" t="s">
+      <c r="H5" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="I5" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J5" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="L5" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="M5" s="19" t="s">
+      <c r="K5" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="N5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="19" t="s">
+      <c r="L5" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="N5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R5" s="23" t="n">
+      <c r="Q5" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" s="24" t="n">
         <v>1680</v>
       </c>
-      <c r="S5" s="23" t="n">
+      <c r="S5" s="24" t="n">
         <v>1680</v>
       </c>
-      <c r="T5" s="24" t="n">
+      <c r="T5" s="25" t="n">
         <v>4500</v>
       </c>
-      <c r="U5" s="23" t="n">
+      <c r="U5" s="24" t="n">
         <v>4500</v>
       </c>
-      <c r="V5" s="23" t="n">
+      <c r="V5" s="24" t="n">
         <v>4800</v>
       </c>
       <c r="W5" s="8" t="n">
@@ -3670,68 +3705,68 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="B6" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="C6" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="20" t="str">
+      <c r="F6" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="21" t="str">
         <f aca="false">B6&amp;" | место "&amp;E6</f>
         <v>UZ95-039-2026 | место 2</v>
       </c>
-      <c r="H6" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="21" t="s">
+      <c r="H6" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="I6" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="L6" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="M6" s="19" t="s">
+      <c r="K6" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="N6" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="19" t="s">
+      <c r="L6" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="Q6" s="19" t="s">
+      <c r="N6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R6" s="23" t="n">
+      <c r="Q6" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R6" s="24" t="n">
         <v>1680</v>
       </c>
-      <c r="S6" s="23" t="n">
+      <c r="S6" s="24" t="n">
         <v>1680</v>
       </c>
-      <c r="T6" s="24" t="n">
+      <c r="T6" s="25" t="n">
         <v>4500</v>
       </c>
-      <c r="U6" s="23" t="n">
+      <c r="U6" s="24" t="n">
         <v>4500</v>
       </c>
-      <c r="V6" s="23" t="n">
+      <c r="V6" s="24" t="n">
         <v>4800</v>
       </c>
       <c r="W6" s="8" t="n">
@@ -3775,68 +3810,68 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="B7" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="C7" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="20" t="str">
+      <c r="E7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="21" t="str">
         <f aca="false">B7&amp;" | место "&amp;E7</f>
         <v>UZ95-040-2026 | место 1</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="21" t="s">
+      <c r="H7" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="I7" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="L7" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N7" s="22" t="n">
+      <c r="K7" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="L7" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="22" t="n">
+      <c r="O7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="P7" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q7" s="19" t="s">
+      <c r="P7" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R7" s="23" t="n">
+      <c r="Q7" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R7" s="24" t="n">
         <v>760</v>
       </c>
-      <c r="S7" s="23" t="n">
+      <c r="S7" s="24" t="n">
         <v>2280</v>
       </c>
-      <c r="T7" s="24" t="n">
+      <c r="T7" s="25" t="n">
         <v>685</v>
       </c>
-      <c r="U7" s="23" t="n">
+      <c r="U7" s="24" t="n">
         <v>2055</v>
       </c>
-      <c r="V7" s="23" t="n">
+      <c r="V7" s="24" t="n">
         <v>2305</v>
       </c>
       <c r="W7" s="8" t="n">
@@ -3880,68 +3915,68 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="19" t="s">
+      <c r="B8" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="C8" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="20" t="str">
+      <c r="F8" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="21" t="str">
         <f aca="false">B8&amp;" | место "&amp;E8</f>
         <v>UZ95-040-2026 | место 2</v>
       </c>
-      <c r="H8" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="21" t="s">
+      <c r="H8" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="I8" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M8" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="22" t="n">
+      <c r="K8" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="O8" s="22" t="n">
+      <c r="O8" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="P8" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q8" s="19" t="s">
+      <c r="P8" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R8" s="23" t="n">
+      <c r="Q8" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R8" s="24" t="n">
         <v>760</v>
       </c>
-      <c r="S8" s="23" t="n">
+      <c r="S8" s="24" t="n">
         <v>2280</v>
       </c>
-      <c r="T8" s="24" t="n">
+      <c r="T8" s="25" t="n">
         <v>685</v>
       </c>
-      <c r="U8" s="23" t="n">
+      <c r="U8" s="24" t="n">
         <v>2055</v>
       </c>
-      <c r="V8" s="23" t="n">
+      <c r="V8" s="24" t="n">
         <v>2305</v>
       </c>
       <c r="W8" s="8" t="n">
@@ -3985,68 +4020,68 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="B9" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="C9" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="20" t="str">
+      <c r="F9" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="21" t="str">
         <f aca="false">B9&amp;" | место "&amp;E9</f>
         <v>UZ95-040-2026 | место 3</v>
       </c>
-      <c r="H9" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="21" t="s">
+      <c r="H9" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="I9" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="L9" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="N9" s="22" t="n">
+      <c r="K9" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="O9" s="22" t="n">
+      <c r="O9" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="P9" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q9" s="19" t="s">
+      <c r="P9" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R9" s="23" t="n">
+      <c r="Q9" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R9" s="24" t="n">
         <v>760</v>
       </c>
-      <c r="S9" s="23" t="n">
+      <c r="S9" s="24" t="n">
         <v>2280</v>
       </c>
-      <c r="T9" s="24" t="n">
+      <c r="T9" s="25" t="n">
         <v>685</v>
       </c>
-      <c r="U9" s="23" t="n">
+      <c r="U9" s="24" t="n">
         <v>2055</v>
       </c>
-      <c r="V9" s="23" t="n">
+      <c r="V9" s="24" t="n">
         <v>2305</v>
       </c>
       <c r="W9" s="8" t="n">
@@ -4090,68 +4125,68 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="19" t="s">
+      <c r="B10" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="C10" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="20" t="str">
+      <c r="E10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="21" t="str">
         <f aca="false">B10&amp;" | место "&amp;E10</f>
         <v>UZ95-041-2026 | место 1</v>
       </c>
-      <c r="H10" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="21" t="s">
+      <c r="H10" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="I10" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="M10" s="19" t="s">
+      <c r="K10" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="N10" s="22" t="n">
+      <c r="L10" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N10" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="O10" s="22" t="n">
+      <c r="O10" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="P10" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q10" s="19" t="s">
+      <c r="P10" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R10" s="23" t="n">
+      <c r="Q10" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R10" s="24" t="n">
         <v>102</v>
       </c>
-      <c r="S10" s="23" t="n">
+      <c r="S10" s="24" t="n">
         <v>714</v>
       </c>
-      <c r="T10" s="24" t="n">
+      <c r="T10" s="25" t="n">
         <v>1.8</v>
       </c>
-      <c r="U10" s="23" t="n">
+      <c r="U10" s="24" t="n">
         <v>12.6</v>
       </c>
-      <c r="V10" s="23" t="n">
+      <c r="V10" s="24" t="n">
         <v>75</v>
       </c>
       <c r="W10" s="8" t="n">
@@ -4195,68 +4230,68 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="C11" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="20" t="str">
+      <c r="E11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="21" t="str">
         <f aca="false">B11&amp;" | место "&amp;E11</f>
         <v>UZ95-041-2026 | место 1</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="L11" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="I11" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N11" s="22" t="n">
+      <c r="N11" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O11" s="22" t="n">
+      <c r="O11" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P11" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q11" s="19" t="s">
+      <c r="P11" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R11" s="23" t="n">
+      <c r="Q11" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R11" s="24" t="n">
         <v>471</v>
       </c>
-      <c r="S11" s="23" t="n">
+      <c r="S11" s="24" t="n">
         <v>942</v>
       </c>
-      <c r="T11" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="23" t="n">
+      <c r="T11" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="23" t="n">
+      <c r="V11" s="24" t="n">
         <v>75</v>
       </c>
       <c r="W11" s="8" t="n">
@@ -4300,68 +4335,68 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="19" t="s">
+      <c r="B12" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="C12" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="20" t="str">
+      <c r="E12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="21" t="str">
         <f aca="false">B12&amp;" | место "&amp;E12</f>
         <v>UZ95-041-2026 | место 1</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="21" t="s">
+      <c r="H12" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="I12" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="L12" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q12" s="19" t="s">
+      <c r="K12" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R12" s="23" t="n">
+      <c r="Q12" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R12" s="24" t="n">
         <v>185</v>
       </c>
-      <c r="S12" s="23" t="n">
+      <c r="S12" s="24" t="n">
         <v>185</v>
       </c>
-      <c r="T12" s="24" t="n">
+      <c r="T12" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="U12" s="23" t="n">
+      <c r="U12" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="V12" s="23" t="n">
+      <c r="V12" s="24" t="n">
         <v>75</v>
       </c>
       <c r="W12" s="8" t="n">
@@ -4405,68 +4440,68 @@
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="C13" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="20" t="str">
+      <c r="E13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="21" t="str">
         <f aca="false">B13&amp;" | место "&amp;E13</f>
         <v>UZ95-041-2026 | место 1</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="J13" s="21" t="s">
+      <c r="H13" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="I13" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N13" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q13" s="19" t="s">
+      <c r="K13" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="L13" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R13" s="23" t="n">
+      <c r="Q13" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R13" s="24" t="n">
         <v>471</v>
       </c>
-      <c r="S13" s="23" t="n">
+      <c r="S13" s="24" t="n">
         <v>471</v>
       </c>
-      <c r="T13" s="24" t="n">
+      <c r="T13" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="U13" s="23" t="n">
+      <c r="U13" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="V13" s="23" t="n">
+      <c r="V13" s="24" t="n">
         <v>75</v>
       </c>
       <c r="W13" s="8" t="n">
@@ -4510,68 +4545,68 @@
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="B14" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="C14" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="20" t="str">
+      <c r="E14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="21" t="str">
         <f aca="false">B14&amp;" | место "&amp;E14</f>
         <v>UZ95-041-2026 | место 1</v>
       </c>
-      <c r="H14" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="J14" s="21" t="s">
+      <c r="H14" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="I14" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="L14" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="M14" s="19" t="s">
+      <c r="K14" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="N14" s="22" t="n">
+      <c r="L14" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="N14" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="O14" s="22" t="n">
+      <c r="O14" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q14" s="19" t="s">
+      <c r="P14" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R14" s="23" t="n">
+      <c r="Q14" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R14" s="24" t="n">
         <v>240</v>
       </c>
-      <c r="S14" s="23" t="n">
+      <c r="S14" s="24" t="n">
         <v>720</v>
       </c>
-      <c r="T14" s="24" t="n">
+      <c r="T14" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="U14" s="23" t="n">
+      <c r="U14" s="24" t="n">
         <v>1.2</v>
       </c>
-      <c r="V14" s="23" t="n">
+      <c r="V14" s="24" t="n">
         <v>75</v>
       </c>
       <c r="W14" s="8" t="n">
@@ -4615,68 +4650,68 @@
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="B15" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="C15" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="20" t="str">
+      <c r="E15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="21" t="str">
         <f aca="false">B15&amp;" | место "&amp;E15</f>
         <v>UZ95-041-2026 | место 1</v>
       </c>
-      <c r="H15" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="21" t="s">
+      <c r="H15" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="K15" s="21" t="s">
+      <c r="I15" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L15" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="M15" s="19" t="s">
+      <c r="K15" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="N15" s="22" t="n">
+      <c r="L15" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="N15" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="O15" s="22" t="n">
+      <c r="O15" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="P15" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q15" s="19" t="s">
+      <c r="P15" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R15" s="23" t="n">
+      <c r="Q15" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R15" s="24" t="n">
         <v>312</v>
       </c>
-      <c r="S15" s="23" t="n">
+      <c r="S15" s="24" t="n">
         <v>1872</v>
       </c>
-      <c r="T15" s="24" t="n">
+      <c r="T15" s="25" t="n">
         <v>4.5</v>
       </c>
-      <c r="U15" s="23" t="n">
+      <c r="U15" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="V15" s="23" t="n">
+      <c r="V15" s="24" t="n">
         <v>75</v>
       </c>
       <c r="W15" s="8" t="n">
@@ -4720,68 +4755,68 @@
       <c r="A16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="B16" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="C16" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="20" t="str">
+      <c r="F16" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="21" t="str">
         <f aca="false">B16&amp;" | место "&amp;E16</f>
         <v>UZ95-042-2026 | место 0</v>
       </c>
-      <c r="H16" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" s="21" t="s">
+      <c r="H16" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="K16" s="21" t="s">
+      <c r="I16" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="J16" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="L16" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="M16" s="19" t="s">
+      <c r="K16" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="N16" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q16" s="19" t="s">
+      <c r="L16" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="N16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R16" s="23" t="n">
+      <c r="Q16" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R16" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="S16" s="23" t="n">
+      <c r="S16" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="T16" s="24" t="n">
+      <c r="T16" s="25" t="n">
         <v>0.5</v>
       </c>
-      <c r="U16" s="23" t="n">
+      <c r="U16" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="V16" s="23" t="n">
+      <c r="V16" s="24" t="n">
         <v>10</v>
       </c>
       <c r="W16" s="8" t="n">
@@ -4825,68 +4860,68 @@
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="19" t="s">
+      <c r="B17" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="C17" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="20" t="str">
+      <c r="F17" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="21" t="str">
         <f aca="false">B17&amp;" | место "&amp;E17</f>
         <v>UZ95-042-2026 | место 0</v>
       </c>
-      <c r="H17" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="J17" s="21" t="s">
+      <c r="H17" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="K17" s="21" t="s">
+      <c r="I17" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="L17" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="M17" s="19" t="s">
+      <c r="K17" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="N17" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q17" s="19" t="s">
+      <c r="L17" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="N17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R17" s="23" t="n">
+      <c r="Q17" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R17" s="24" t="n">
         <v>1550</v>
       </c>
-      <c r="S17" s="23" t="n">
+      <c r="S17" s="24" t="n">
         <v>1550</v>
       </c>
-      <c r="T17" s="24" t="n">
+      <c r="T17" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="U17" s="23" t="n">
+      <c r="U17" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="23" t="n">
+      <c r="V17" s="24" t="n">
         <v>10</v>
       </c>
       <c r="W17" s="8" t="n">
@@ -4930,68 +4965,68 @@
       <c r="A18" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="19" t="s">
+      <c r="B18" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="C18" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="20" t="str">
+      <c r="F18" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="21" t="str">
         <f aca="false">B18&amp;" | место "&amp;E18</f>
         <v>UZ95-042-2026 | место 0</v>
       </c>
-      <c r="H18" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="J18" s="21" t="s">
+      <c r="H18" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="K18" s="21" t="s">
+      <c r="I18" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="J18" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="L18" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="N18" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q18" s="19" t="s">
+      <c r="K18" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="N18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R18" s="23" t="n">
+      <c r="Q18" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R18" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="S18" s="23" t="n">
+      <c r="S18" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="T18" s="24" t="n">
+      <c r="T18" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="U18" s="23" t="n">
+      <c r="U18" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="23" t="n">
+      <c r="V18" s="24" t="n">
         <v>10</v>
       </c>
       <c r="W18" s="8" t="n">
@@ -5035,68 +5070,68 @@
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="B19" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="19" t="s">
+      <c r="C19" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="20" t="str">
+      <c r="D19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="21" t="str">
         <f aca="false">B19&amp;" | место "&amp;E19</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H19" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="J19" s="21" t="s">
+      <c r="H19" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="K19" s="21" t="s">
+      <c r="I19" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="L19" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N19" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q19" s="19" t="s">
+      <c r="K19" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R19" s="23" t="n">
+      <c r="Q19" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R19" s="24" t="n">
         <v>347</v>
       </c>
-      <c r="S19" s="23" t="n">
+      <c r="S19" s="24" t="n">
         <v>347</v>
       </c>
-      <c r="T19" s="24" t="n">
+      <c r="T19" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="U19" s="23" t="n">
+      <c r="U19" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="V19" s="23" t="n">
+      <c r="V19" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W19" s="8" t="n">
@@ -5140,68 +5175,68 @@
       <c r="A20" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="B20" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="19" t="s">
+      <c r="C20" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G20" s="20" t="str">
+      <c r="D20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="21" t="str">
         <f aca="false">B20&amp;" | место "&amp;E20</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H20" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="J20" s="21" t="s">
+      <c r="H20" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="K20" s="21" t="s">
+      <c r="I20" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="L20" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="M20" s="19" t="s">
+      <c r="K20" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="N20" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q20" s="19" t="s">
+      <c r="L20" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="N20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R20" s="23" t="n">
+      <c r="Q20" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" s="24" t="n">
         <v>735.92</v>
       </c>
-      <c r="S20" s="23" t="n">
+      <c r="S20" s="24" t="n">
         <v>735.92</v>
       </c>
-      <c r="T20" s="24" t="n">
+      <c r="T20" s="25" t="n">
         <v>2.4</v>
       </c>
-      <c r="U20" s="23" t="n">
+      <c r="U20" s="24" t="n">
         <v>2.4</v>
       </c>
-      <c r="V20" s="23" t="n">
+      <c r="V20" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W20" s="8" t="n">
@@ -5245,68 +5280,68 @@
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="19" t="s">
+      <c r="B21" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="19" t="s">
+      <c r="C21" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="20" t="str">
+      <c r="D21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="21" t="str">
         <f aca="false">B21&amp;" | место "&amp;E21</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H21" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="J21" s="21" t="s">
+      <c r="H21" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="K21" s="21" t="s">
+      <c r="I21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="L21" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="M21" s="19" t="s">
+      <c r="K21" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="N21" s="22" t="n">
+      <c r="L21" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="N21" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="O21" s="22" t="n">
+      <c r="O21" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="P21" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q21" s="19" t="s">
+      <c r="P21" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R21" s="23" t="n">
+      <c r="Q21" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R21" s="24" t="n">
         <v>950</v>
       </c>
-      <c r="S21" s="23" t="n">
+      <c r="S21" s="24" t="n">
         <v>2850</v>
       </c>
-      <c r="T21" s="24" t="n">
+      <c r="T21" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="U21" s="23" t="n">
+      <c r="U21" s="24" t="n">
         <v>78</v>
       </c>
-      <c r="V21" s="23" t="n">
+      <c r="V21" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W21" s="8" t="n">
@@ -5350,68 +5385,68 @@
       <c r="A22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="B22" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="19" t="s">
+      <c r="C22" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="20" t="str">
+      <c r="D22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="21" t="str">
         <f aca="false">B22&amp;" | место "&amp;E22</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H22" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="J22" s="21" t="s">
+      <c r="H22" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="K22" s="21" t="s">
+      <c r="I22" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="J22" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="L22" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="M22" s="19" t="s">
+      <c r="K22" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="N22" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q22" s="19" t="s">
+      <c r="L22" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="N22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R22" s="23" t="n">
+      <c r="Q22" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R22" s="24" t="n">
         <v>841.71</v>
       </c>
-      <c r="S22" s="23" t="n">
+      <c r="S22" s="24" t="n">
         <v>841.71</v>
       </c>
-      <c r="T22" s="24" t="n">
+      <c r="T22" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="U22" s="23" t="n">
+      <c r="U22" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="V22" s="23" t="n">
+      <c r="V22" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W22" s="8" t="n">
@@ -5455,68 +5490,68 @@
       <c r="A23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="B23" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="19" t="s">
+      <c r="C23" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="20" t="str">
+      <c r="D23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="21" t="str">
         <f aca="false">B23&amp;" | место "&amp;E23</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H23" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="J23" s="21" t="s">
+      <c r="H23" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="K23" s="21" t="s">
+      <c r="I23" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="J23" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="L23" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="N23" s="22" t="n">
+      <c r="K23" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="N23" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O23" s="22" t="n">
+      <c r="O23" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P23" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q23" s="19" t="s">
+      <c r="P23" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R23" s="23" t="n">
+      <c r="Q23" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R23" s="24" t="n">
         <v>590.65</v>
       </c>
-      <c r="S23" s="23" t="n">
+      <c r="S23" s="24" t="n">
         <v>1181.3</v>
       </c>
-      <c r="T23" s="24" t="n">
+      <c r="T23" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="U23" s="23" t="n">
+      <c r="U23" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="V23" s="23" t="n">
+      <c r="V23" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W23" s="8" t="n">
@@ -5560,68 +5595,68 @@
       <c r="A24" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="B24" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="19" t="s">
+      <c r="C24" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="20" t="str">
+      <c r="D24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="21" t="str">
         <f aca="false">B24&amp;" | место "&amp;E24</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H24" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="J24" s="21" t="s">
+      <c r="H24" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="K24" s="21" t="s">
+      <c r="I24" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="L24" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="M24" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N24" s="22" t="n">
+      <c r="K24" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="L24" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N24" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="22" t="n">
+      <c r="O24" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P24" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q24" s="19" t="s">
+      <c r="P24" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R24" s="23" t="n">
+      <c r="Q24" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R24" s="24" t="n">
         <v>471</v>
       </c>
-      <c r="S24" s="23" t="n">
+      <c r="S24" s="24" t="n">
         <v>942</v>
       </c>
-      <c r="T24" s="24" t="n">
+      <c r="T24" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="U24" s="23" t="n">
+      <c r="U24" s="24" t="n">
         <v>0.4</v>
       </c>
-      <c r="V24" s="23" t="n">
+      <c r="V24" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W24" s="8" t="n">
@@ -5665,68 +5700,68 @@
       <c r="A25" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="19" t="s">
+      <c r="B25" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="19" t="s">
+      <c r="C25" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G25" s="20" t="str">
+      <c r="D25" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="21" t="str">
         <f aca="false">B25&amp;" | место "&amp;E25</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H25" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="J25" s="21" t="s">
+      <c r="H25" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="K25" s="21" t="s">
+      <c r="I25" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="J25" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="L25" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="M25" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="N25" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q25" s="19" t="s">
+      <c r="K25" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="L25" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="N25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R25" s="23" t="n">
+      <c r="Q25" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R25" s="24" t="n">
         <v>386.02</v>
       </c>
-      <c r="S25" s="23" t="n">
+      <c r="S25" s="24" t="n">
         <v>386.02</v>
       </c>
-      <c r="T25" s="24" t="n">
+      <c r="T25" s="25" t="n">
         <v>0.2</v>
       </c>
-      <c r="U25" s="23" t="n">
+      <c r="U25" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="V25" s="23" t="n">
+      <c r="V25" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W25" s="8" t="n">
@@ -5770,68 +5805,68 @@
       <c r="A26" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="19" t="s">
+      <c r="B26" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="19" t="s">
+      <c r="C26" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="20" t="str">
+      <c r="D26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="21" t="str">
         <f aca="false">B26&amp;" | место "&amp;E26</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H26" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J26" s="21" t="s">
+      <c r="H26" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="K26" s="21" t="s">
+      <c r="I26" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="J26" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="L26" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="M26" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="N26" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q26" s="19" t="s">
+      <c r="K26" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="N26" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R26" s="23" t="n">
+      <c r="Q26" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R26" s="24" t="n">
         <v>204</v>
       </c>
-      <c r="S26" s="23" t="n">
+      <c r="S26" s="24" t="n">
         <v>204</v>
       </c>
-      <c r="T26" s="24" t="n">
+      <c r="T26" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="U26" s="23" t="n">
+      <c r="U26" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="V26" s="23" t="n">
+      <c r="V26" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W26" s="8" t="n">
@@ -5875,68 +5910,68 @@
       <c r="A27" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="19" t="s">
+      <c r="B27" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="19" t="s">
+      <c r="C27" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G27" s="20" t="str">
+      <c r="D27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="21" t="str">
         <f aca="false">B27&amp;" | место "&amp;E27</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H27" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="J27" s="21" t="s">
+      <c r="H27" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="K27" s="21" t="s">
+      <c r="I27" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J27" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="L27" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="M27" s="19" t="s">
+      <c r="K27" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="N27" s="22" t="n">
+      <c r="L27" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="N27" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="O27" s="22" t="n">
+      <c r="O27" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="P27" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q27" s="19" t="s">
+      <c r="P27" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R27" s="23" t="n">
+      <c r="Q27" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R27" s="24" t="n">
         <v>496.75</v>
       </c>
-      <c r="S27" s="23" t="n">
+      <c r="S27" s="24" t="n">
         <v>1987</v>
       </c>
-      <c r="T27" s="24" t="n">
+      <c r="T27" s="25" t="n">
         <v>0.8</v>
       </c>
-      <c r="U27" s="23" t="n">
+      <c r="U27" s="24" t="n">
         <v>3.2</v>
       </c>
-      <c r="V27" s="23" t="n">
+      <c r="V27" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W27" s="8" t="n">
@@ -5980,68 +6015,68 @@
       <c r="A28" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="19" t="s">
+      <c r="B28" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="19" t="s">
+      <c r="C28" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G28" s="20" t="str">
+      <c r="D28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="21" t="str">
         <f aca="false">B28&amp;" | место "&amp;E28</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H28" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="I28" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="J28" s="21" t="s">
+      <c r="H28" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="K28" s="21" t="s">
+      <c r="I28" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="J28" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="L28" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="M28" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N28" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q28" s="19" t="s">
+      <c r="K28" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="L28" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R28" s="23" t="n">
+      <c r="Q28" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R28" s="24" t="n">
         <v>497.2</v>
       </c>
-      <c r="S28" s="23" t="n">
+      <c r="S28" s="24" t="n">
         <v>497.2</v>
       </c>
-      <c r="T28" s="24" t="n">
+      <c r="T28" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="U28" s="23" t="n">
+      <c r="U28" s="24" t="n">
         <v>0.4</v>
       </c>
-      <c r="V28" s="23" t="n">
+      <c r="V28" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W28" s="8" t="n">
@@ -6085,68 +6120,68 @@
       <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G29" s="20" t="str">
+      <c r="D29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="21" t="str">
         <f aca="false">B29&amp;" | место "&amp;E29</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H29" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="J29" s="21" t="s">
+      <c r="H29" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="K29" s="21" t="s">
+      <c r="I29" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="J29" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="L29" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="M29" s="19" t="s">
+      <c r="K29" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="N29" s="22" t="n">
+      <c r="L29" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="N29" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O29" s="22" t="n">
+      <c r="O29" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P29" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q29" s="19" t="s">
+      <c r="P29" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R29" s="23" t="n">
+      <c r="Q29" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R29" s="24" t="n">
         <v>1200</v>
       </c>
-      <c r="S29" s="23" t="n">
+      <c r="S29" s="24" t="n">
         <v>2400</v>
       </c>
-      <c r="T29" s="24" t="n">
+      <c r="T29" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="U29" s="23" t="n">
+      <c r="U29" s="24" t="n">
         <v>62</v>
       </c>
-      <c r="V29" s="23" t="n">
+      <c r="V29" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W29" s="8" t="n">
@@ -6190,68 +6225,68 @@
       <c r="A30" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G30" s="20" t="str">
+      <c r="D30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="21" t="str">
         <f aca="false">B30&amp;" | место "&amp;E30</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H30" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="I30" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="J30" s="21" t="s">
+      <c r="H30" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="K30" s="21" t="s">
+      <c r="I30" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="J30" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="L30" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="M30" s="19" t="s">
+      <c r="K30" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="N30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q30" s="19" t="s">
+      <c r="L30" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="N30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R30" s="23" t="n">
+      <c r="Q30" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R30" s="24" t="n">
         <v>845</v>
       </c>
-      <c r="S30" s="23" t="n">
+      <c r="S30" s="24" t="n">
         <v>845</v>
       </c>
-      <c r="T30" s="24" t="n">
+      <c r="T30" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="U30" s="23" t="n">
+      <c r="U30" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="V30" s="23" t="n">
+      <c r="V30" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W30" s="8" t="n">
@@ -6295,68 +6330,68 @@
       <c r="A31" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="19" t="s">
+      <c r="B31" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="19" t="s">
+      <c r="C31" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="20" t="str">
+      <c r="D31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G31" s="21" t="str">
         <f aca="false">B31&amp;" | место "&amp;E31</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H31" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="J31" s="21" t="s">
+      <c r="H31" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="K31" s="21" t="s">
+      <c r="I31" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="J31" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="L31" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="M31" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N31" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q31" s="19" t="s">
+      <c r="K31" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="L31" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="N31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R31" s="23" t="n">
+      <c r="Q31" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R31" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="S31" s="23" t="n">
+      <c r="S31" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="T31" s="24" t="n">
+      <c r="T31" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="U31" s="23" t="n">
+      <c r="U31" s="24" t="n">
         <v>0.3</v>
       </c>
-      <c r="V31" s="23" t="n">
+      <c r="V31" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W31" s="8" t="n">
@@ -6400,68 +6435,68 @@
       <c r="A32" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="19" t="s">
+      <c r="B32" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="19" t="s">
+      <c r="C32" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="G32" s="20" t="str">
+      <c r="D32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" s="21" t="str">
         <f aca="false">B32&amp;" | место "&amp;E32</f>
         <v>UZ95-043-2026 | место 1</v>
       </c>
-      <c r="H32" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="J32" s="21" t="s">
+      <c r="H32" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="K32" s="21" t="s">
+      <c r="I32" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="J32" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="L32" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="M32" s="19" t="s">
+      <c r="K32" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="N32" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q32" s="19" t="s">
+      <c r="L32" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="N32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R32" s="23" t="n">
+      <c r="Q32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R32" s="24" t="n">
         <v>148.56</v>
       </c>
-      <c r="S32" s="23" t="n">
+      <c r="S32" s="24" t="n">
         <v>148.56</v>
       </c>
-      <c r="T32" s="24" t="n">
+      <c r="T32" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="U32" s="23" t="n">
+      <c r="U32" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="V32" s="23" t="n">
+      <c r="V32" s="24" t="n">
         <v>235</v>
       </c>
       <c r="W32" s="8" t="n">
@@ -6505,68 +6540,68 @@
       <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C33" s="19" t="s">
+      <c r="B33" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="C33" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G33" s="20" t="str">
+      <c r="E33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G33" s="21" t="str">
         <f aca="false">B33&amp;" | место "&amp;E33</f>
         <v>UZ95-044-2026 | место 1</v>
       </c>
-      <c r="H33" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="J33" s="21" t="s">
+      <c r="H33" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="K33" s="21" t="s">
+      <c r="I33" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="J33" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="L33" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="M33" s="19" t="s">
+      <c r="K33" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="N33" s="22" t="n">
+      <c r="L33" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="N33" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="O33" s="22" t="n">
+      <c r="O33" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="P33" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q33" s="19" t="s">
+      <c r="P33" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R33" s="23" t="n">
+      <c r="Q33" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R33" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="S33" s="23" t="n">
+      <c r="S33" s="24" t="n">
         <v>760</v>
       </c>
-      <c r="T33" s="24" t="n">
+      <c r="T33" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="U33" s="23" t="n">
+      <c r="U33" s="24" t="n">
         <v>228</v>
       </c>
-      <c r="V33" s="23" t="n">
+      <c r="V33" s="24" t="n">
         <v>370</v>
       </c>
       <c r="W33" s="8" t="n">
@@ -6610,68 +6645,68 @@
       <c r="A34" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="B34" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D34" s="19" t="n">
+      <c r="C34" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G34" s="20" t="str">
+      <c r="E34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G34" s="21" t="str">
         <f aca="false">B34&amp;" | место "&amp;E34</f>
         <v>UZ95-044-2026 | место 1</v>
       </c>
-      <c r="H34" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="J34" s="21" t="s">
+      <c r="H34" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="K34" s="21" t="s">
+      <c r="I34" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="J34" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="L34" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="M34" s="19" t="s">
+      <c r="K34" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="N34" s="22" t="n">
+      <c r="L34" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N34" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="O34" s="22" t="n">
+      <c r="O34" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="P34" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q34" s="19" t="s">
+      <c r="P34" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R34" s="23" t="n">
+      <c r="Q34" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R34" s="24" t="n">
         <v>39</v>
       </c>
-      <c r="S34" s="23" t="n">
+      <c r="S34" s="24" t="n">
         <v>390</v>
       </c>
-      <c r="T34" s="24" t="n">
+      <c r="T34" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="U34" s="23" t="n">
+      <c r="U34" s="24" t="n">
         <v>120</v>
       </c>
-      <c r="V34" s="23" t="n">
+      <c r="V34" s="24" t="n">
         <v>370</v>
       </c>
       <c r="W34" s="8" t="n">
@@ -6715,68 +6750,68 @@
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C35" s="19" t="s">
+      <c r="B35" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="C35" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G35" s="20" t="str">
+      <c r="E35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G35" s="21" t="str">
         <f aca="false">B35&amp;" | место "&amp;E35</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H35" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="J35" s="21" t="s">
+      <c r="H35" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="K35" s="21" t="s">
+      <c r="I35" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J35" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="L35" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="M35" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N35" s="22" t="n">
+      <c r="K35" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="L35" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N35" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O35" s="22" t="n">
+      <c r="O35" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P35" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q35" s="19" t="s">
+      <c r="P35" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R35" s="23" t="n">
+      <c r="Q35" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R35" s="24" t="n">
         <v>83.77</v>
       </c>
-      <c r="S35" s="23" t="n">
+      <c r="S35" s="24" t="n">
         <v>167.54</v>
       </c>
-      <c r="T35" s="24" t="n">
+      <c r="T35" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="U35" s="23" t="n">
+      <c r="U35" s="24" t="n">
         <v>46</v>
       </c>
-      <c r="V35" s="23" t="n">
+      <c r="V35" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W35" s="8" t="n">
@@ -6820,68 +6855,68 @@
       <c r="A36" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C36" s="19" t="s">
+      <c r="B36" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="C36" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G36" s="20" t="str">
+      <c r="E36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G36" s="21" t="str">
         <f aca="false">B36&amp;" | место "&amp;E36</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H36" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="J36" s="21" t="s">
+      <c r="H36" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="K36" s="21" t="s">
+      <c r="I36" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="J36" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="L36" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="M36" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N36" s="22" t="n">
+      <c r="K36" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="L36" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N36" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O36" s="22" t="n">
+      <c r="O36" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P36" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q36" s="19" t="s">
+      <c r="P36" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R36" s="23" t="n">
+      <c r="Q36" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R36" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="S36" s="23" t="n">
+      <c r="S36" s="24" t="n">
         <v>144</v>
       </c>
-      <c r="T36" s="24" t="n">
+      <c r="T36" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="U36" s="23" t="n">
+      <c r="U36" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="V36" s="23" t="n">
+      <c r="V36" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W36" s="8" t="n">
@@ -6925,68 +6960,68 @@
       <c r="A37" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C37" s="19" t="s">
+      <c r="B37" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D37" s="19" t="n">
+      <c r="C37" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G37" s="20" t="str">
+      <c r="E37" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" s="21" t="str">
         <f aca="false">B37&amp;" | место "&amp;E37</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H37" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="I37" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="J37" s="21" t="s">
+      <c r="H37" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="I37" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="L37" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="M37" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q37" s="19" t="s">
+      <c r="K37" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="L37" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R37" s="23" t="n">
+      <c r="Q37" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R37" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="S37" s="23" t="n">
+      <c r="S37" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="T37" s="24" t="n">
+      <c r="T37" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="U37" s="23" t="n">
+      <c r="U37" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="V37" s="23" t="n">
+      <c r="V37" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W37" s="8" t="n">
@@ -7030,68 +7065,68 @@
       <c r="A38" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="C38" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D38" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G38" s="20" t="str">
+      <c r="E38" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G38" s="21" t="str">
         <f aca="false">B38&amp;" | место "&amp;E38</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="K38" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="L38" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="J38" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="K38" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L38" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="M38" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="N38" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q38" s="19" t="s">
+      <c r="M38" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="N38" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R38" s="23" t="n">
+      <c r="Q38" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R38" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="S38" s="23" t="n">
+      <c r="S38" s="24" t="n">
         <v>47</v>
       </c>
-      <c r="T38" s="24" t="n">
+      <c r="T38" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="U38" s="23" t="n">
+      <c r="U38" s="24" t="n">
         <v>23</v>
       </c>
-      <c r="V38" s="23" t="n">
+      <c r="V38" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W38" s="8" t="n">
@@ -7135,68 +7170,68 @@
       <c r="A39" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C39" s="19" t="s">
+      <c r="B39" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="C39" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G39" s="20" t="str">
+      <c r="E39" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G39" s="21" t="str">
         <f aca="false">B39&amp;" | место "&amp;E39</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H39" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="I39" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="J39" s="21" t="s">
+      <c r="H39" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="K39" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L39" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="M39" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N39" s="22" t="n">
+      <c r="I39" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="J39" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="K39" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="L39" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N39" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O39" s="22" t="n">
+      <c r="O39" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P39" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q39" s="19" t="s">
+      <c r="P39" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R39" s="23" t="n">
+      <c r="Q39" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R39" s="24" t="n">
         <v>89</v>
       </c>
-      <c r="S39" s="23" t="n">
+      <c r="S39" s="24" t="n">
         <v>178</v>
       </c>
-      <c r="T39" s="24" t="n">
+      <c r="T39" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="U39" s="23" t="n">
+      <c r="U39" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="V39" s="23" t="n">
+      <c r="V39" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W39" s="8" t="n">
@@ -7240,68 +7275,68 @@
       <c r="A40" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C40" s="19" t="s">
+      <c r="B40" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D40" s="19" t="n">
+      <c r="C40" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G40" s="20" t="str">
+      <c r="E40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G40" s="21" t="str">
         <f aca="false">B40&amp;" | место "&amp;E40</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="I40" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="J40" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="I40" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="J40" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="K40" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L40" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="M40" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N40" s="22" t="n">
+      <c r="K40" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="L40" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N40" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="O40" s="22" t="n">
+      <c r="O40" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="P40" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q40" s="19" t="s">
+      <c r="P40" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R40" s="23" t="n">
+      <c r="Q40" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R40" s="24" t="n">
         <v>89</v>
       </c>
-      <c r="S40" s="23" t="n">
+      <c r="S40" s="24" t="n">
         <v>178</v>
       </c>
-      <c r="T40" s="24" t="n">
+      <c r="T40" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="U40" s="23" t="n">
+      <c r="U40" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="V40" s="23" t="n">
+      <c r="V40" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W40" s="8" t="n">
@@ -7345,68 +7380,68 @@
       <c r="A41" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C41" s="19" t="s">
+      <c r="B41" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D41" s="19" t="n">
+      <c r="C41" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D41" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G41" s="20" t="str">
+      <c r="E41" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G41" s="21" t="str">
         <f aca="false">B41&amp;" | место "&amp;E41</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H41" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="J41" s="21" t="s">
+      <c r="H41" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="K41" s="21" t="s">
+      <c r="I41" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="J41" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="L41" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="M41" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="N41" s="22" t="n">
+      <c r="K41" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="L41" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="N41" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="O41" s="22" t="n">
+      <c r="O41" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="P41" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q41" s="19" t="s">
+      <c r="P41" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R41" s="23" t="n">
+      <c r="Q41" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R41" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="S41" s="23" t="n">
+      <c r="S41" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="T41" s="24" t="n">
+      <c r="T41" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="U41" s="23" t="n">
+      <c r="U41" s="24" t="n">
         <v>120</v>
       </c>
-      <c r="V41" s="23" t="n">
+      <c r="V41" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W41" s="8" t="n">
@@ -7450,68 +7485,68 @@
       <c r="A42" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C42" s="19" t="s">
+      <c r="B42" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D42" s="19" t="n">
+      <c r="C42" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D42" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G42" s="20" t="str">
+      <c r="E42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G42" s="21" t="str">
         <f aca="false">B42&amp;" | место "&amp;E42</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H42" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="J42" s="21" t="s">
+      <c r="H42" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="K42" s="21" t="s">
+      <c r="I42" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="J42" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="L42" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="M42" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="N42" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q42" s="19" t="s">
+      <c r="K42" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="L42" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="N42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R42" s="23" t="n">
+      <c r="Q42" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R42" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="S42" s="23" t="n">
+      <c r="S42" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="T42" s="24" t="n">
+      <c r="T42" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="U42" s="23" t="n">
+      <c r="U42" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="V42" s="23" t="n">
+      <c r="V42" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W42" s="8" t="n">
@@ -7555,68 +7590,68 @@
       <c r="A43" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C43" s="19" t="s">
+      <c r="B43" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D43" s="19" t="n">
+      <c r="C43" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D43" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G43" s="20" t="str">
+      <c r="E43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G43" s="21" t="str">
         <f aca="false">B43&amp;" | место "&amp;E43</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H43" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="I43" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="J43" s="21" t="s">
+      <c r="H43" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="K43" s="21" t="s">
+      <c r="I43" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="J43" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="L43" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="M43" s="19" t="s">
+      <c r="K43" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="N43" s="22" t="n">
+      <c r="L43" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="N43" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="O43" s="22" t="n">
+      <c r="O43" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="P43" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q43" s="19" t="s">
+      <c r="P43" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R43" s="23" t="n">
+      <c r="Q43" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R43" s="24" t="n">
         <v>138</v>
       </c>
-      <c r="S43" s="23" t="n">
+      <c r="S43" s="24" t="n">
         <v>2208</v>
       </c>
-      <c r="T43" s="24" t="n">
+      <c r="T43" s="25" t="n">
         <v>2.5</v>
       </c>
-      <c r="U43" s="23" t="n">
+      <c r="U43" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="V43" s="23" t="n">
+      <c r="V43" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W43" s="8" t="n">
@@ -7660,68 +7695,68 @@
       <c r="A44" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C44" s="19" t="s">
+      <c r="B44" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D44" s="19" t="n">
+      <c r="C44" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D44" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E44" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="G44" s="20" t="str">
+      <c r="E44" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G44" s="21" t="str">
         <f aca="false">B44&amp;" | место "&amp;E44</f>
         <v>UZ95-045-2026 | место 1</v>
       </c>
-      <c r="H44" s="19" t="s">
+      <c r="H44" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="J44" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="K44" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="L44" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="M44" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="I44" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="J44" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="K44" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="L44" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="M44" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="N44" s="22" t="n">
+      <c r="N44" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="O44" s="22" t="n">
+      <c r="O44" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="P44" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q44" s="19" t="s">
+      <c r="P44" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="R44" s="23" t="n">
+      <c r="Q44" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R44" s="24" t="n">
         <v>138</v>
       </c>
-      <c r="S44" s="23" t="n">
+      <c r="S44" s="24" t="n">
         <v>966</v>
       </c>
-      <c r="T44" s="24" t="n">
+      <c r="T44" s="25" t="n">
         <v>2.5</v>
       </c>
-      <c r="U44" s="23" t="n">
+      <c r="U44" s="24" t="n">
         <v>17.5</v>
       </c>
-      <c r="V44" s="23" t="n">
+      <c r="V44" s="24" t="n">
         <v>460</v>
       </c>
       <c r="W44" s="8" t="n">
@@ -7763,8 +7798,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AE44"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7797,12 +7833,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>203</v>
+      <c r="A2" s="26" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7810,70 +7846,70 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="B5" s="27" t="n">
         <f aca="false">COUNTIF(Товары!$B$5:$B$44,A5)</f>
         <v>2</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="n">
         <f aca="false">SUMIFS(Товары!$F$5:$F$44,Товары!$B$5:$B$44,A5)</f>
         <v>2</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="23" t="n">
+      <c r="F5" s="24" t="n">
         <v>3360</v>
       </c>
       <c r="G5" s="8" t="n">
@@ -7884,7 +7920,7 @@
         <f aca="false">ROUND(G5-F5,2)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="23" t="n">
+      <c r="I5" s="24" t="n">
         <v>9000</v>
       </c>
       <c r="J5" s="8" t="n">
@@ -7895,7 +7931,7 @@
         <f aca="false">ROUND(J5-I5,2)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="23" t="n">
+      <c r="L5" s="24" t="n">
         <v>9600</v>
       </c>
       <c r="M5" s="8" t="n">
@@ -7917,23 +7953,23 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="B6" s="27" t="n">
         <f aca="false">COUNTIF(Товары!$B$5:$B$44,A6)</f>
         <v>3</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>9</v>
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">SUMIFS(Товары!$F$5:$F$44,Товары!$B$5:$B$44,A6)</f>
         <v>9</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="24" t="n">
         <v>6840</v>
       </c>
       <c r="G6" s="8" t="n">
@@ -7944,7 +7980,7 @@
         <f aca="false">ROUND(G6-F6,2)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="24" t="n">
         <v>6165</v>
       </c>
       <c r="J6" s="8" t="n">
@@ -7955,7 +7991,7 @@
         <f aca="false">ROUND(J6-I6,2)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="23" t="n">
+      <c r="L6" s="24" t="n">
         <v>6915</v>
       </c>
       <c r="M6" s="8" t="n">
@@ -7977,23 +8013,23 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="B7" s="27" t="n">
         <f aca="false">COUNTIF(Товары!$B$5:$B$44,A7)</f>
         <v>6</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>20</v>
       </c>
       <c r="D7" s="7" t="n">
         <f aca="false">SUMIFS(Товары!$F$5:$F$44,Товары!$B$5:$B$44,A7)</f>
         <v>20</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="24" t="n">
         <v>4904</v>
       </c>
       <c r="G7" s="8" t="n">
@@ -8004,7 +8040,7 @@
         <f aca="false">ROUND(G7-F7,2)</f>
         <v>0</v>
       </c>
-      <c r="I7" s="23" t="n">
+      <c r="I7" s="24" t="n">
         <v>43.25</v>
       </c>
       <c r="J7" s="8" t="n">
@@ -8015,7 +8051,7 @@
         <f aca="false">ROUND(J7-I7,2)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="23" t="n">
+      <c r="L7" s="24" t="n">
         <v>75</v>
       </c>
       <c r="M7" s="8" t="n">
@@ -8037,23 +8073,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="B8" s="27" t="n">
         <f aca="false">COUNTIF(Товары!$B$5:$B$44,A8)</f>
         <v>3</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="7" t="n">
         <f aca="false">SUMIFS(Товары!$F$5:$F$44,Товары!$B$5:$B$44,A8)</f>
         <v>3</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="24" t="n">
         <v>1990</v>
       </c>
       <c r="G8" s="8" t="n">
@@ -8064,7 +8100,7 @@
         <f aca="false">ROUND(G8-F8,2)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="23" t="n">
+      <c r="I8" s="24" t="n">
         <v>7.5</v>
       </c>
       <c r="J8" s="8" t="n">
@@ -8075,7 +8111,7 @@
         <f aca="false">ROUND(J8-I8,2)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="23" t="n">
+      <c r="L8" s="24" t="n">
         <v>10</v>
       </c>
       <c r="M8" s="8" t="n">
@@ -8097,23 +8133,23 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="B9" s="27" t="n">
         <f aca="false">COUNTIF(Товары!$B$5:$B$44,A9)</f>
         <v>14</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <v>22</v>
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">SUMIFS(Товары!$F$5:$F$44,Товары!$B$5:$B$44,A9)</f>
         <v>22</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="24" t="n">
         <v>13567.15</v>
       </c>
       <c r="G9" s="8" t="n">
@@ -8124,7 +8160,7 @@
         <f aca="false">ROUND(G9-F9,2)</f>
         <v>148.56</v>
       </c>
-      <c r="I9" s="23" t="n">
+      <c r="I9" s="24" t="n">
         <v>191.7</v>
       </c>
       <c r="J9" s="8" t="n">
@@ -8135,7 +8171,7 @@
         <f aca="false">ROUND(J9-I9,2)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="23" t="n">
+      <c r="L9" s="24" t="n">
         <v>235</v>
       </c>
       <c r="M9" s="8" t="n">
@@ -8157,23 +8193,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B10" s="26" t="n">
+        <v>165</v>
+      </c>
+      <c r="B10" s="27" t="n">
         <f aca="false">COUNTIF(Товары!$B$5:$B$44,A10)</f>
         <v>2</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <v>29</v>
       </c>
       <c r="D10" s="7" t="n">
         <f aca="false">SUMIFS(Товары!$F$5:$F$44,Товары!$B$5:$B$44,A10)</f>
         <v>29</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="24" t="n">
         <v>1150</v>
       </c>
       <c r="G10" s="8" t="n">
@@ -8184,7 +8220,7 @@
         <f aca="false">ROUND(G10-F10,2)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="23" t="n">
+      <c r="I10" s="24" t="n">
         <v>348</v>
       </c>
       <c r="J10" s="8" t="n">
@@ -8195,7 +8231,7 @@
         <f aca="false">ROUND(J10-I10,2)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="23" t="n">
+      <c r="L10" s="24" t="n">
         <v>370</v>
       </c>
       <c r="M10" s="8" t="n">
@@ -8217,23 +8253,23 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="26" t="n">
+        <v>176</v>
+      </c>
+      <c r="B11" s="27" t="n">
         <f aca="false">COUNTIF(Товары!$B$5:$B$44,A11)</f>
         <v>10</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <v>44</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">SUMIFS(Товары!$F$5:$F$44,Товары!$B$5:$B$44,A11)</f>
         <v>44</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="23" t="n">
         <v>44</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="24" t="n">
         <v>4320.54</v>
       </c>
       <c r="G11" s="8" t="n">
@@ -8244,7 +8280,7 @@
         <f aca="false">ROUND(G11-F11,2)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="24" t="n">
         <v>439.5</v>
       </c>
       <c r="J11" s="8" t="n">
@@ -8255,7 +8291,7 @@
         <f aca="false">ROUND(J11-I11,2)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="24" t="n">
         <v>460</v>
       </c>
       <c r="M11" s="8" t="n">
@@ -8276,173 +8312,173 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="28" t="n">
+      <c r="A12" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="29" t="n">
         <f aca="false">SUM(B5:B11)</f>
         <v>40</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="30" t="n">
         <f aca="false">SUM(C5:C11)</f>
         <v>129</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <f aca="false">SUM(D5:D11)</f>
         <v>129</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="30" t="n">
         <f aca="false">SUM(E5:E11)</f>
         <v>129</v>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="31" t="n">
         <f aca="false">SUM(F5:F11)</f>
         <v>36131.69</v>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="31" t="n">
         <f aca="false">SUM(G5:G11)</f>
         <v>36280.25</v>
       </c>
-      <c r="H12" s="30" t="n">
+      <c r="H12" s="31" t="n">
         <f aca="false">ROUND(G12-F12,2)</f>
         <v>148.56</v>
       </c>
-      <c r="I12" s="30" t="n">
+      <c r="I12" s="31" t="n">
         <f aca="false">SUM(I5:I11)</f>
         <v>16194.95</v>
       </c>
-      <c r="J12" s="30" t="n">
+      <c r="J12" s="31" t="n">
         <f aca="false">SUM(J5:J11)</f>
         <v>16194.95</v>
       </c>
-      <c r="K12" s="30" t="n">
+      <c r="K12" s="31" t="n">
         <f aca="false">ROUND(J12-I12,2)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="30" t="n">
+      <c r="L12" s="31" t="n">
         <f aca="false">SUM(L5:L11)</f>
         <v>17665</v>
       </c>
-      <c r="M12" s="30" t="n">
+      <c r="M12" s="31" t="n">
         <f aca="false">SUM(M5:M11)</f>
         <v>17665</v>
       </c>
-      <c r="N12" s="30" t="n">
+      <c r="N12" s="31" t="n">
         <f aca="false">ROUND(M12-L12,2)</f>
         <v>0</v>
       </c>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27" t="str">
+      <c r="O12" s="28"/>
+      <c r="P12" s="28" t="str">
         <f aca="false">IF(COUNTIF(P5:P11,"OK")=7,"OK","РАСХОЖДЕНИЕ")</f>
         <v>РАСХОЖДЕНИЕ</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="s">
-        <v>220</v>
+      <c r="A15" s="32" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="33" t="n">
+      <c r="A16" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34" t="n">
         <f aca="false">COUNTIF('Исходные данные'!AA5:AA44,"ОШИБКА")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="33" t="n">
+      <c r="A17" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="34" t="n">
         <f aca="false">COUNTIF('Исходные данные'!AB5:AB44,"ОШИБКА")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33" t="n">
+      <c r="A18" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34" t="n">
         <f aca="false">COUNTIF('Исходные данные'!AC5:AC44,"ОШИБКА")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33" t="n">
+      <c r="A19" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34" t="n">
         <f aca="false">COUNTIF('Исходные данные'!AD5:AD44,"ОШИБКА")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33" t="n">
+      <c r="A20" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="34" t="n">
         <f aca="false">COUNTIF('Исходные данные'!AE5:AE44,"ОШИБКА")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33" t="n">
+      <c r="A21" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34" t="n">
         <f aca="false">SUMPRODUCT(--(LEN('Исходные данные'!M5:M44)&lt;&gt;10))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="33" t="n">
+      <c r="A22" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34" t="n">
         <f aca="false">COUNTIF(Товары!$H$5:$H$44,"&lt;=0")+COUNTIF(Товары!$I$5:$I$44,"&lt;=0")+COUNTIF(Товары!$J$5:$J$44,"&lt;=0")</f>
         <v>0</v>
       </c>
@@ -8486,12 +8522,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8505,183 +8541,183 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>236</v>
+      <c r="B5" s="35" t="s">
+        <v>237</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>240</v>
+      <c r="B6" s="36" t="s">
+        <v>241</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="35" t="s">
-        <v>240</v>
+      <c r="B7" s="36" t="s">
+        <v>241</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>240</v>
+      <c r="B8" s="36" t="s">
+        <v>241</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>240</v>
+      <c r="B9" s="36" t="s">
+        <v>241</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>240</v>
+      <c r="B10" s="36" t="s">
+        <v>241</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>240</v>
+      <c r="B11" s="36" t="s">
+        <v>241</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8689,22 +8725,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8712,22 +8748,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8735,22 +8771,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8758,22 +8794,22 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8781,22 +8817,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8804,22 +8840,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
